--- a/teacher_evaluation_forms/006_simple_instructor_evaluation_form_template--teacher_evaluation_forms.xlsx
+++ b/teacher_evaluation_forms/006_simple_instructor_evaluation_form_template--teacher_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>instructor_name</t>
+          <t>Instructor Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>course_name</t>
+          <t>Course Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>course_instructor_rating</t>
+          <t>Course Instructor Rating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>course_materials</t>
+          <t>Course Materials</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>course_clarity</t>
+          <t>Course Clarity</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>course_helpfulness</t>
+          <t>Course Helpfulness</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>course_instructor_supportiveness</t>
+          <t>Course Instructor Supportiveness</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>course_instructor_clarity</t>
+          <t>Course Instructor Clarity</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>course_instructor_helpfulness</t>
+          <t>Course Instructor Helpfulness</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -732,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>course_instructor_will</t>
+          <t>Course Instructor Will</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -755,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>course_instructor_joy</t>
+          <t>Course Instructor Joy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -778,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction</t>
+          <t>Course Instructor Satisfaction</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -801,13 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>course_instructor_effectiveness</t>
+          <t>Course Instructor Effectiveness</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -824,13 +824,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>Course Instructor Punctuality</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -847,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>Course Instructor Willingness</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>course_instructor_joyfulness</t>
+          <t>Course Instructor Joyfulness</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -888,18 +888,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction</t>
+          <t>course_instructor_satisfying</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction</t>
+          <t>Course Instructor Satisfying</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -911,18 +911,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>course_instructor_joy</t>
+          <t>course_instructor_joy_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>course_instructor_joy</t>
+          <t>Course Instructor Joy 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -934,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>course_instructor_punctuality_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>Course Instructor Punctuality 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -957,18 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>course_instructor_willingness_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>Course Instructor Willingness 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -980,18 +980,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>course_instructor_punctuality_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>Course Instructor Punctuality 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>course_instructor_willingness_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>Course Instructor Willingness 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1026,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>course_instructor_punctuality_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality</t>
+          <t>Course Instructor Punctuality 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1049,18 +1049,18 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>course_instructor_willingness_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>course_instructor_willingness</t>
+          <t>Course Instructor Willingness 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfactory',_'label':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfactory', 'label': 'Very Satisfactory'}</t>
+          <t>Very Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'satisfactory',_'label':_'satisfactory'}</t>
+          <t>satisfactory</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'satisfactory', 'label': 'Satisfactory'}</t>
+          <t>Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'unsatisfactory',_'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'unsatisfactory', 'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'clear',_'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'clear', 'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'not_clear',_'label':_'not_clear'}</t>
+          <t>not_clear</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'not_clear', 'label': 'Not clear'}</t>
+          <t>Not Clear</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'unclear',_'label':_'unclear'}</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'unclear', 'label': 'Unclear'}</t>
+          <t>Unclear</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'very_supportive',_'label':_'very_supportive'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'very_supportive', 'label': 'Very Supportive'}</t>
+          <t>Very Supportive</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_supportive',_'label':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_supportive', 'label': 'Somewhat Supportive'}</t>
+          <t>Somewhat Supportive</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'not_supportive',_'label':_'not_supportive'}</t>
+          <t>not_supportive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'not_supportive', 'label': 'Not Supportive'}</t>
+          <t>Not Supportive</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'clear',_'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'clear', 'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'unclear',_'label':_'unclear'}</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'unclear', 'label': 'Unclear'}</t>
+          <t>Unclear</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'very_unclear',_'label':_'very_unclear'}</t>
+          <t>very_unclear</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'very_unclear', 'label': 'Very Unclear'}</t>
+          <t>Very Unclear</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'helpful',_'label':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'helpful', 'label': 'Helpful'}</t>
+          <t>Helpful</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_helpful',_'label':_'not_helpful'}</t>
+          <t>not_helpful</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'not_helpful', 'label': 'Not helpful'}</t>
+          <t>Not Helpful</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'very_willing',_'label':_'very_willing'}</t>
+          <t>very_willing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'very_willing', 'label': 'Very Willing'}</t>
+          <t>Very Willing</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_willing',_'label':_'somewhat_willing'}</t>
+          <t>somewhat_willing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_willing', 'label': 'Somewhat Willing'}</t>
+          <t>Somewhat Willing</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_willing',_'label':_'not_willing'}</t>
+          <t>not_willing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'not_willing', 'label': 'Not Willing'}</t>
+          <t>Not Willing</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'very_joyful',_'label':_'very_joyful'}</t>
+          <t>very_joyful</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'very_joyful', 'label': 'Very Joyful'}</t>
+          <t>Very Joyful</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_joyful',_'label':_'somewhat_joyful'}</t>
+          <t>somewhat_joyful</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_joyful', 'label': 'Somewhat Joyful'}</t>
+          <t>Somewhat Joyful</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'not_joyful',_'label':_'not_joyful'}</t>
+          <t>not_joyful</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'not_joyful', 'label': 'Not Joyful'}</t>
+          <t>Not Joyful</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'very_effective',_'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'very_effective', 'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_effective',_'label':_'somewhat_effective'}</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_effective', 'label': 'Somewhat Effective'}</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'not_effective',_'label':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'not_effective', 'label': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'punctual',_'label':_'punctual'}</t>
+          <t>punctual</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'punctual', 'label': 'Punctual'}</t>
+          <t>Punctual</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'not_punctual',_'label':_'not_punctual'}</t>
+          <t>not_punctual</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'not_punctual', 'label': 'Not Punctual'}</t>
+          <t>Not Punctual</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'very_punctual',_'label':_'very_punctual'}</t>
+          <t>very_punctual</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'very_punctual', 'label': 'Very Punctual'}</t>
+          <t>Very Punctual</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'willing',_'label':_'willing'}</t>
+          <t>willful</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'willing', 'label': 'Willing'}</t>
+          <t>Willful</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'not_willing',_'label':_'not_willing'}</t>
+          <t>not_willful</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'not_willing', 'label': 'Not Willing'}</t>
+          <t>Not Willful</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'very_willing',_'label':_'very_willing'}</t>
+          <t>very_willful</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'very_willing', 'label': 'Very Willing'}</t>
+          <t>Very Willful</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'joyfull',_'label':_'joyfull'}</t>
+          <t>joyfull</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'joyfull', 'label': 'Joyfull'}</t>
+          <t>Joyfull</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'not_joyful',_'label':_'not_joyful'}</t>
+          <t>not_joyful</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'not_joyful', 'label': 'Not Joyful'}</t>
+          <t>Not Joyful</t>
         </is>
       </c>
     </row>
@@ -1635,420 +1635,420 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'very_joyful',_'label':_'very_joyful'}</t>
+          <t>very_joyful</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'very_joyful', 'label': 'Very Joyful'}</t>
+          <t>Very Joyful</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction_choices</t>
+          <t>course_instructor_satisfying_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfying',_'label':_'very_satisfying'}</t>
+          <t>very_satisfying</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfying', 'label': 'Very Satisfying'}</t>
+          <t>Very Satisfying</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction_choices</t>
+          <t>course_instructor_satisfying_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfying',_'label':_'somewhat_satisfying'}</t>
+          <t>somewhat_satisfying</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfying', 'label': 'Somewhat Satisfying'}</t>
+          <t>Somewhat Satisfying</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>course_instructor_satisfaction_choices</t>
+          <t>course_instructor_satisfying_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'not_satisfying',_'label':_'not_satisfying'}</t>
+          <t>not_satisfying</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'not_satisfying', 'label': 'Not Satisfying'}</t>
+          <t>Not Satisfying</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>course_instructor_joy_choices</t>
+          <t>course_instructor_joy_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'joyful',_'label':_'joyful'}</t>
+          <t>joyful</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'joyful', 'label': 'Joyful'}</t>
+          <t>Joyful</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>course_instructor_joy_choices</t>
+          <t>course_instructor_joy_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'not_joyful',_'label':_'not_joyful'}</t>
+          <t>not_joyful</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'not_joyful', 'label': 'Not Joyful'}</t>
+          <t>Not Joyful</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>course_instructor_joy_choices</t>
+          <t>course_instructor_joy_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'very_joyful',_'label':_'very_joyful'}</t>
+          <t>very_joyful</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'very_joyful', 'label': 'Very Joyful'}</t>
+          <t>Very Joyful</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'punctual',_'label':_'punctual'}</t>
+          <t>punctual</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'punctual', 'label': 'Punctual'}</t>
+          <t>Punctual</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'not_punctual',_'label':_'not_punctual'}</t>
+          <t>not_punctual</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'not_punctual', 'label': 'Not Punctual'}</t>
+          <t>Not Punctual</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'very_punctual',_'label':_'very_punctual'}</t>
+          <t>very_punctual</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'very_punctual', 'label': 'Very Punctual'}</t>
+          <t>Very Punctual</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'willful',_'label':_'willful'}</t>
+          <t>willful</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'willful', 'label': 'Willful'}</t>
+          <t>Willful</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'not_willful',_'label':_'not_willful'}</t>
+          <t>not_willful</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'not_willful', 'label': 'Not Willful'}</t>
+          <t>Not Willful</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'very_willful',_'label':_'very_willful'}</t>
+          <t>very_willful</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'very_willful', 'label': 'Very Willful'}</t>
+          <t>Very Willful</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'punctual',_'label':_'punctual'}</t>
+          <t>punctual</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'punctual', 'label': 'Punctual'}</t>
+          <t>Punctual</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_3_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'not_punctual',_'label':_'not_punctual'}</t>
+          <t>not_punctual</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'not_punctual', 'label': 'Not Punctual'}</t>
+          <t>Not Punctual</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_3_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'very_punctual',_'label':_'very_punctual'}</t>
+          <t>very_punctual</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'very_punctual', 'label': 'Very Punctual'}</t>
+          <t>Very Punctual</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_3_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'willful',_'label':_'willful'}</t>
+          <t>willful</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'willful', 'label': 'Willful'}</t>
+          <t>Willful</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_3_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'not_willful',_'label':_'not_willful'}</t>
+          <t>not_willful</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'not_willful', 'label': 'Not Willful'}</t>
+          <t>Not Willful</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_3_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'very_willful',_'label':_'very_willful'}</t>
+          <t>very_willful</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'very_willful', 'label': 'Very Willful'}</t>
+          <t>Very Willful</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_4_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'punctual',_'label':_'punctual'}</t>
+          <t>punctual</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'punctual', 'label': 'Punctual'}</t>
+          <t>Punctual</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_4_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'not_punctual',_'label':_'not_punctual'}</t>
+          <t>not_punctual</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'not_punctual', 'label': 'Not Punctual'}</t>
+          <t>Not Punctual</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>course_instructor_punctuality_choices</t>
+          <t>course_instructor_punctuality_4_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'very_punctual',_'label':_'very_punctual'}</t>
+          <t>very_punctual</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'very_punctual', 'label': 'Very Punctual'}</t>
+          <t>Very Punctual</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_4_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'willful',_'label':_'willful'}</t>
+          <t>willful</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'willful', 'label': 'Willful'}</t>
+          <t>Willful</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_4_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'not_willful',_'label':_'not_willful'}</t>
+          <t>not_willful</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'not_willful', 'label': 'Not Willful'}</t>
+          <t>Not Willful</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>course_instructor_willingness_choices</t>
+          <t>course_instructor_willingness_4_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'very_willful',_'label':_'very_willful'}</t>
+          <t>very_willful</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'very_willful', 'label': 'Very Willful'}</t>
+          <t>Very Willful</t>
         </is>
       </c>
     </row>
